--- a/rmonize/data_dictionary/DD_NAKO_P1.xlsx
+++ b/rmonize/data_dictionary/DD_NAKO_P1.xlsx
@@ -383,7 +383,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/rmonize/data_dictionary/DD_NAKO_P1.xlsx
+++ b/rmonize/data_dictionary/DD_NAKO_P1.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>gcal</t>
+          <t>a_nu_gcal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">

--- a/rmonize/data_dictionary/DD_NAKO_P1.xlsx
+++ b/rmonize/data_dictionary/DD_NAKO_P1.xlsx
@@ -804,7 +804,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -823,6 +823,11 @@
           <t>label</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -838,6 +843,11 @@
           <t>Mannlich</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -853,19 +863,29 @@
           <t>Weiblich</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>a_ses_isced11_level</t>
+          <t>basis_sex</t>
         </is>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Less than primary education (Not applicable for Germany)</t>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -876,11 +896,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Primary education</t>
+          <t>Less than primary education (Not applicable for Germany)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -891,11 +916,16 @@
         </is>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lower secondary education</t>
+          <t>Primary education</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -906,11 +936,16 @@
         </is>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Upper secondary education</t>
+          <t>Lower secondary education</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -921,11 +956,16 @@
         </is>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Post-secondary non-tertiary education</t>
+          <t>Upper secondary education</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -936,11 +976,16 @@
         </is>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Short-cycle tertiary education (Not applicable for Germany)</t>
+          <t>Post-secondary non-tertiary education</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -951,11 +996,16 @@
         </is>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bachelor's or equivalent level</t>
+          <t>Short-cycle tertiary education (Not applicable for Germany)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -966,11 +1016,16 @@
         </is>
       </c>
       <c r="B11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Master's or equivalent level</t>
+          <t>Bachelor's or equivalent level</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -981,71 +1036,356 @@
         </is>
       </c>
       <c r="B12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Doctoral or equivalent level</t>
+          <t>Master's or equivalent level</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>a_smok_stat_qn</t>
+          <t>a_ses_isced11_level</t>
         </is>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kein Raucher, auch nicht ehemalig</t>
+          <t>Doctoral or equivalent level</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>a_smok_stat_qn</t>
+          <t>a_ses_isced11_level</t>
         </is>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ehemaliger Raucher</t>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>a_smok_stat_qn</t>
+          <t>a_ses_isced11_level</t>
         </is>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>-9</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Raucher</t>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>a_ses_isced11_level</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>-88</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>still in general-education school training and without a vocational qualification</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>a_ses_isced11_level</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>-99</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>still in vocational training</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>a_gpaq_ptotalmet</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>777777</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>a_smok_stat_qn</t>
         </is>
       </c>
-      <c r="B16">
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Kein Raucher, auch nicht ehemalig</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>a_smok_stat_qn</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>2</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ehemaliger Raucher</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>a_smok_stat_qn</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>3</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Raucher</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>a_smok_stat_qn</t>
+        </is>
+      </c>
+      <c r="B22">
         <v>4</v>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Rauchstatus unbekannt</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>a_anthro_bmi</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>7777</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>missing due to impossible calculation</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>a_anthro_bmi</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>8886</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Implausible information</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>a_anthro_bmi</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>7776</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Calculation not possible due to implausible values</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>a_anthro_bmi</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>7775</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Allowed skipped</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>a_anthro_bmi</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>8888</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>a_anthro_bmi</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>9999</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Don't know</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>a_anthro_bmi</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>8889</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Not specified, erroneously skipped</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
